--- a/Result/profitability/2514.xlsx
+++ b/Result/profitability/2514.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.37625</v>
+        <v>0.1262499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>10.0675</v>
+        <v>9.96125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22375</v>
+        <v>0.06249999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>9.625</v>
+        <v>9.7875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1174999999999999</v>
+        <v>-0.08375000000000007</v>
       </c>
       <c r="N4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.407499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.83</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3025000000000001</v>
+        <v>-0.4712500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7675</v>
+        <v>6.59875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2725000000000001</v>
+        <v>-0.4862500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>5.14625</v>
+        <v>5.131250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3500000000000001</v>
+        <v>-0.5362500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>3.72875</v>
+        <v>3.59125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3012500000000001</v>
+        <v>-0.48875</v>
       </c>
       <c r="N8" t="n">
-        <v>2.61125</v>
+        <v>2.4575</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5031</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4421</v>
+      </c>
+      <c r="E75" t="n">
+        <v>610</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-709</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-738</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-389</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.85125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.571428571428572</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.229999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09206586826347296</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1001483679525222</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
